--- a/vlearn-app/public/quiz_excel/Day_08_RAG Pipeline _ Retrieval Evaluation/Day_08_Phan_02_19_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_08_RAG Pipeline _ Retrieval Evaluation/Day_08_Phan_02_19_Cau.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
@@ -648,7 +648,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bước hợp các candidate chưa phải là fusion và không được làm mất tín hiệu của từng đường xử lý.</t>
+          <t>Khi hợp nhất các ứng viên từ hai đường xử lý dense và sparse trước bước reranking, danh sách ứng viên phải giữ đầy đủ: (a) ID ổn định của bản ghi để tránh trùng lặp; (b) Thứ hạng và điểm dense; (c) Thứ hạng và điểm sparse; (d) Dấu vết nguồn (lineage) của từng đường xử lý. Không được giữ hai bản ghi trùng ID hay chỉ giữ điểm số lớn hơn.</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4,5</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -799,7 +799,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp dụng công thức có trọng số và chú ý hệ số `(1 - alpha)` của sparse.</t>
+          <t>Điểm kết hợp: `alpha × dense + (1 - alpha) × sparse` với alpha = 0,6. Với A (dense=0,9, sparse=0,2): điểm = 0,6×0,9 + 0,4×0,2 = 0,54 + 0,08 = 0,62 (mệnh đề a đúng). Với B (dense=0,5, sparse=0,8): điểm = 0,6×0,5 + 0,4×0,8 = 0,30 + 0,32 = 0,62 (mệnh đề b đúng). Hai kết quả có điểm bằng nhau nên hòa và cần dùng quy tắc phá hòa đã khai báo (mệnh đề d đúng). Alpha = 0,6 biểu thị dense đóng góp 60% và sparse đóng góp 40% (mệnh đề e đúng). Mệnh đề c sai vì hai ứng viên có cùng điểm tổng.</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -854,7 +854,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt Weighted formula và Một-trừ-alpha.</t>
+          <t>Với công thức `alpha × dense + (1 - alpha) × sparse` trên candidate có dense=0,2 và sparse=0,9: (a) Khi alpha = 0, điểm = 0 + 1×0,9 = 0,9 và chỉ có tín hiệu sparse được dùng; (b) Khi alpha = 1, điểm = 1×0,2 + 0 = 0,2 và chỉ có tín hiệu dense được dùng; (d) Việc kiểm tra hai điểm biên giá trị (boundary testing) là bước xác minh tính đúng đắn kỹ thuật, tách biệt với việc điều chỉnh tham số alpha tối ưu trên benchmark thực nghiệm.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o4 → o5 → o3 → o1</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -957,7 +957,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Fallback phải có điều kiện vào và điều kiện dừng.</t>
+          <t>Trình tự luồng xử lý dự phòng (fallback workflow) có điều kiện vào và điểm dừng rõ ràng: 1. Chạy đường xử lý chính (dense retrieval) (o2) -&gt; 2. Kiểm tra điều kiện kích hoạt có thể quan sát (ví dụ điểm số dưới ngưỡng chất lượng) (o4) -&gt; 3. Chạy đường xử lý dự phòng (BM25) (o5) -&gt; 4. Ghi nhận và giữ nguyên dấu vết nguồn của đường xử lý/kết quả (o3) -&gt; 5. Kết thúc bằng thông báo không có bằng chứng nếu đường dự phòng cũng thất bại (o1).</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1264,7 +1264,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một khối tốt phải ánh xạ ngược được tới bản ghi gốc và không làm thay đổi thứ bậc chỉ dẫn.</t>
+          <t>Để định dạng ngữ cảnh (context) có cấu trúc chặt chẽ bảo vệ mô hình khỏi prompt injection và trích dẫn chuẩn: (a) Tách bạch rõ ràng giữa quy tắc hệ thống, câu hỏi của người dùng và dữ liệu đã truy xuất; (b) Sử dụng delimiter phân cách riêng biệt cho từng bản ghi tài liệu; (c) Giữ nguyên đầy đủ doc_id, nguồn, vị trí trang, phiên bản và nội dung văn bản; (d) Giữ thứ tự tài liệu xác định và có thể tái lập.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
@@ -1319,7 +1319,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm từng vế câu hỏi đã có nguồn riêng hay chưa.</t>
+          <t>Gói bằng chứng đầy đủ (evidence bundle) cho câu hỏi đa thuộc tính cần chứng minh: (a) Ánh xạ điều kiện tới tài liệu A; (b) Ánh xạ hạn chót tới tài liệu B; (c) Ánh xạ người phê duyệt tới tài liệu C; (d) Lưu giữ nguồn và vị trí chính xác cho từng dữ kiện độc lập. Không được gộp chung hay chỉ trích dẫn tài liệu đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1518,7 +1518,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Khả năng phân giải ID và mức độ hỗ trợ của bằng chứng là hai phép kiểm khác nhau.</t>
+          <t>Quy tắc gắn nhãn trích dẫn (citation) chính xác ở cấp độ mệnh đề nguyên tử: (a) Gắn [D1] ngay sau mệnh đề về hạn chót; (b) Gắn [D2] ngay sau mệnh đề về người phê duyệt; (c) Xác minh rằng D1 và D2 thực sự tồn tại trong context gửi cho model; (d) Kiểm tra từng khối bằng chứng có thực sự hỗ trợ ngữ nghĩa cho mệnh đề tương ứng hay không. Không đặt một citation chung ở cuối đoạn.</t>
         </is>
       </c>
     </row>
